--- a/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>3592.608</v>
+        <v>3977.61</v>
       </c>
       <c r="C4">
-        <v>1967.573</v>
+        <v>2844.838</v>
       </c>
       <c r="D4">
-        <v>5217.642</v>
+        <v>5110.382</v>
       </c>
       <c r="E4">
-        <v>5669.363</v>
+        <v>6272.583</v>
       </c>
       <c r="F4">
-        <v>3103.82</v>
+        <v>4462.24</v>
       </c>
       <c r="G4">
-        <v>8234.906000000001</v>
+        <v>8082.925</v>
       </c>
       <c r="H4">
-        <v>168737594.649</v>
+        <v>186820380.809</v>
       </c>
       <c r="I4">
-        <v>92412974.03399999</v>
+        <v>133616349.274</v>
       </c>
       <c r="J4">
-        <v>245062215.263</v>
+        <v>240024412.344</v>
       </c>
       <c r="K4">
-        <v>754025272.08</v>
+        <v>834253480.377</v>
       </c>
       <c r="L4">
-        <v>412808058.965</v>
+        <v>593477876.66</v>
       </c>
       <c r="M4">
-        <v>1095242485.194</v>
+        <v>1075029084.093</v>
       </c>
     </row>
     <row r="5">
@@ -695,13 +695,13 @@
         <v>243799.15</v>
       </c>
       <c r="E8">
-        <v>1212986.999</v>
+        <v>202164.5</v>
       </c>
       <c r="F8">
-        <v>760216.599</v>
+        <v>126702.767</v>
       </c>
       <c r="G8">
-        <v>1665757.399</v>
+        <v>277626.233</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>161327270912.627</v>
+        <v>26887878485.438</v>
       </c>
       <c r="L8">
-        <v>101108807698.558</v>
+        <v>16851467949.76</v>
       </c>
       <c r="M8">
-        <v>221545734126.695</v>
+        <v>36924289021.116</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>206775.857</v>
+        <v>207160.859</v>
       </c>
       <c r="C9">
-        <v>121866.248</v>
+        <v>122743.513</v>
       </c>
       <c r="D9">
-        <v>291685.464</v>
+        <v>291578.204</v>
       </c>
       <c r="E9">
-        <v>1243142.887</v>
+        <v>232923.608</v>
       </c>
       <c r="F9">
-        <v>769513.116</v>
+        <v>137357.704</v>
       </c>
       <c r="G9">
-        <v>1716772.66</v>
+        <v>328489.513</v>
       </c>
       <c r="H9">
-        <v>773597846.7539999</v>
+        <v>791680632.914</v>
       </c>
       <c r="I9">
-        <v>264579157.5109999</v>
+        <v>305782532.751</v>
       </c>
       <c r="J9">
-        <v>1282616535.996</v>
+        <v>1277578733.077</v>
       </c>
       <c r="K9">
-        <v>165338004205.636</v>
+        <v>30978839986.744</v>
       </c>
       <c r="L9">
-        <v>102345244446.932</v>
+        <v>18268574515.829</v>
       </c>
       <c r="M9">
-        <v>228330763964.337</v>
+        <v>43689105457.657</v>
       </c>
     </row>
     <row r="10">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>244342.311</v>
+        <v>244727.313</v>
       </c>
       <c r="C10">
-        <v>147645.51</v>
+        <v>148522.775</v>
       </c>
       <c r="D10">
-        <v>341039.11</v>
+        <v>340931.85</v>
       </c>
       <c r="E10">
-        <v>1587725.092</v>
+        <v>577505.8130000001</v>
       </c>
       <c r="F10">
-        <v>1002624.803</v>
+        <v>370469.391</v>
       </c>
       <c r="G10">
-        <v>2172825.383</v>
+        <v>784542.236</v>
       </c>
       <c r="H10">
-        <v>773597846.7539999</v>
+        <v>791680632.914</v>
       </c>
       <c r="I10">
-        <v>264579157.5109999</v>
+        <v>305782532.751</v>
       </c>
       <c r="J10">
-        <v>1282616535.996</v>
+        <v>1277578733.077</v>
       </c>
       <c r="K10">
-        <v>211167437471.678</v>
+        <v>76808273252.786</v>
       </c>
       <c r="L10">
-        <v>133349098869.056</v>
+        <v>49272428937.953</v>
       </c>
       <c r="M10">
-        <v>288985776074.297</v>
+        <v>104344117567.617</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
@@ -437,13 +437,13 @@
         <v>49353.646</v>
       </c>
       <c r="E2">
-        <v>344582.205</v>
+        <v>57430.368</v>
       </c>
       <c r="F2">
-        <v>233111.687</v>
+        <v>38851.948</v>
       </c>
       <c r="G2">
-        <v>456052.723</v>
+        <v>76008.787</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>45829433266.042</v>
+        <v>7638238877.674</v>
       </c>
       <c r="L2">
-        <v>31003854422.124</v>
+        <v>5167309070.354</v>
       </c>
       <c r="M2">
-        <v>60655012109.96</v>
+        <v>10109168684.993</v>
       </c>
     </row>
     <row r="3">
@@ -480,31 +480,31 @@
         <v>15234.968</v>
       </c>
       <c r="E3">
-        <v>7429.477</v>
+        <v>1529.678</v>
       </c>
       <c r="F3">
-        <v>4046.674</v>
+        <v>833.069</v>
       </c>
       <c r="G3">
-        <v>10812.28</v>
+        <v>2226.287</v>
       </c>
       <c r="H3">
-        <v>219421821.325</v>
+        <v>583734563.5420001</v>
       </c>
       <c r="I3">
-        <v>119853875.861</v>
+        <v>318850921.446</v>
       </c>
       <c r="J3">
-        <v>318989766.789</v>
+        <v>848618205.6390001</v>
       </c>
       <c r="K3">
-        <v>988120503.255</v>
+        <v>203447143.157</v>
       </c>
       <c r="L3">
-        <v>538207705.985</v>
+        <v>110798147.126</v>
       </c>
       <c r="M3">
-        <v>1438033300.525</v>
+        <v>296096139.187</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>3977.61</v>
+        <v>781.931</v>
       </c>
       <c r="C4">
-        <v>2844.838</v>
+        <v>-18.997</v>
       </c>
       <c r="D4">
-        <v>5110.382</v>
+        <v>1582.859</v>
       </c>
       <c r="E4">
-        <v>6272.583</v>
+        <v>209.515</v>
       </c>
       <c r="F4">
-        <v>4462.24</v>
+        <v>-5.752</v>
       </c>
       <c r="G4">
-        <v>8082.925</v>
+        <v>424.782</v>
       </c>
       <c r="H4">
-        <v>186820380.809</v>
+        <v>34473003.125</v>
       </c>
       <c r="I4">
-        <v>133616349.274</v>
+        <v>-837501.088</v>
       </c>
       <c r="J4">
-        <v>240024412.344</v>
+        <v>69783507.337</v>
       </c>
       <c r="K4">
-        <v>834253480.377</v>
+        <v>27865522.939</v>
       </c>
       <c r="L4">
-        <v>593477876.66</v>
+        <v>-764991.6459999999</v>
       </c>
       <c r="M4">
-        <v>1075029084.093</v>
+        <v>56496037.523</v>
       </c>
     </row>
     <row r="5">
@@ -566,31 +566,31 @@
         <v>9903.087</v>
       </c>
       <c r="E5">
-        <v>4791.511</v>
+        <v>798.576</v>
       </c>
       <c r="F5">
-        <v>-120.803</v>
+        <v>-19.954</v>
       </c>
       <c r="G5">
-        <v>9703.825999999999</v>
+        <v>1617.106</v>
       </c>
       <c r="H5">
-        <v>72550697.93000001</v>
+        <v>72545798.50399999</v>
       </c>
       <c r="I5">
-        <v>-1543510.566</v>
+        <v>-1543406.331</v>
       </c>
       <c r="J5">
-        <v>146644906.427</v>
+        <v>146635003.34</v>
       </c>
       <c r="K5">
-        <v>637271028.721</v>
+        <v>106210622.09</v>
       </c>
       <c r="L5">
-        <v>-16066839.994</v>
+        <v>-2653871.699</v>
       </c>
       <c r="M5">
-        <v>1290608897.436</v>
+        <v>215075115.878</v>
       </c>
     </row>
     <row r="6">
@@ -609,31 +609,31 @@
         <v>12576.868</v>
       </c>
       <c r="E6">
-        <v>8778.569</v>
+        <v>1482.707</v>
       </c>
       <c r="F6">
-        <v>150.225</v>
+        <v>25.011</v>
       </c>
       <c r="G6">
-        <v>17406.913</v>
+        <v>2940.403</v>
       </c>
       <c r="H6">
-        <v>231905636.005</v>
+        <v>477612305.779</v>
       </c>
       <c r="I6">
-        <v>4579511.214</v>
+        <v>9431555.645</v>
       </c>
       <c r="J6">
-        <v>459231760.796</v>
+        <v>945793055.914</v>
       </c>
       <c r="K6">
-        <v>1167549691.892</v>
+        <v>197200038.303</v>
       </c>
       <c r="L6">
-        <v>19979933.401</v>
+        <v>3326471.62</v>
       </c>
       <c r="M6">
-        <v>2315119450.383</v>
+        <v>391073604.986</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         <v>4953.749</v>
       </c>
       <c r="E7">
-        <v>3486.968</v>
+        <v>792.965</v>
       </c>
       <c r="F7">
-        <v>2116.601</v>
+        <v>481.228</v>
       </c>
       <c r="G7">
-        <v>4857.336</v>
+        <v>1104.701</v>
       </c>
       <c r="H7">
-        <v>80982096.845</v>
+        <v>59946260.276</v>
       </c>
       <c r="I7">
-        <v>49276306.968</v>
+        <v>36476337.833</v>
       </c>
       <c r="J7">
-        <v>112687886.721</v>
+        <v>83416182.719</v>
       </c>
       <c r="K7">
-        <v>463766797.061</v>
+        <v>105464297.664</v>
       </c>
       <c r="L7">
-        <v>281507890.017</v>
+        <v>64003348.48</v>
       </c>
       <c r="M7">
-        <v>646025704.104</v>
+        <v>146925246.847</v>
       </c>
     </row>
     <row r="8">
@@ -695,13 +695,13 @@
         <v>243799.15</v>
       </c>
       <c r="E8">
-        <v>202164.5</v>
+        <v>202271.477</v>
       </c>
       <c r="F8">
-        <v>126702.767</v>
+        <v>126799.228</v>
       </c>
       <c r="G8">
-        <v>277626.233</v>
+        <v>277743.726</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26887878485.438</v>
+        <v>26902106418.724</v>
       </c>
       <c r="L8">
-        <v>16851467949.76</v>
+        <v>16864297313.579</v>
       </c>
       <c r="M8">
-        <v>36924289021.116</v>
+        <v>36939915523.868</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>207160.859</v>
+        <v>203965.18</v>
       </c>
       <c r="C9">
-        <v>122743.513</v>
+        <v>119879.678</v>
       </c>
       <c r="D9">
-        <v>291578.204</v>
+        <v>288050.681</v>
       </c>
       <c r="E9">
-        <v>232923.608</v>
+        <v>207084.918</v>
       </c>
       <c r="F9">
-        <v>137357.704</v>
+        <v>128112.83</v>
       </c>
       <c r="G9">
-        <v>328489.513</v>
+        <v>286057.005</v>
       </c>
       <c r="H9">
-        <v>791680632.914</v>
+        <v>1228311931.226</v>
       </c>
       <c r="I9">
-        <v>305782532.751</v>
+        <v>362377907.505</v>
       </c>
       <c r="J9">
-        <v>1277578733.077</v>
+        <v>2094245954.949</v>
       </c>
       <c r="K9">
-        <v>30978839986.744</v>
+        <v>27542294042.877</v>
       </c>
       <c r="L9">
-        <v>18268574515.829</v>
+        <v>17039006417.46</v>
       </c>
       <c r="M9">
-        <v>43689105457.657</v>
+        <v>38045581668.28899</v>
       </c>
     </row>
     <row r="10">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>244727.313</v>
+        <v>241531.634</v>
       </c>
       <c r="C10">
-        <v>148522.775</v>
+        <v>145658.94</v>
       </c>
       <c r="D10">
-        <v>340931.85</v>
+        <v>337404.327</v>
       </c>
       <c r="E10">
-        <v>577505.8130000001</v>
+        <v>264515.286</v>
       </c>
       <c r="F10">
-        <v>370469.391</v>
+        <v>166964.778</v>
       </c>
       <c r="G10">
-        <v>784542.236</v>
+        <v>362065.792</v>
       </c>
       <c r="H10">
-        <v>791680632.914</v>
+        <v>1228311931.226</v>
       </c>
       <c r="I10">
-        <v>305782532.751</v>
+        <v>362377907.505</v>
       </c>
       <c r="J10">
-        <v>1277578733.077</v>
+        <v>2094245954.949</v>
       </c>
       <c r="K10">
-        <v>76808273252.786</v>
+        <v>35180532920.55099</v>
       </c>
       <c r="L10">
-        <v>49272428937.953</v>
+        <v>22206315487.814</v>
       </c>
       <c r="M10">
-        <v>104344117567.617</v>
+        <v>48154750353.282</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>37566.454</v>
+        <v>58512.408</v>
       </c>
       <c r="C2">
-        <v>25779.262</v>
+        <v>50068.734</v>
       </c>
       <c r="D2">
-        <v>49353.646</v>
+        <v>66956.083</v>
       </c>
       <c r="E2">
-        <v>57430.368</v>
+        <v>100834.615</v>
       </c>
       <c r="F2">
-        <v>38851.948</v>
+        <v>86898.361</v>
       </c>
       <c r="G2">
-        <v>76008.787</v>
+        <v>114770.87</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>7638238877.674</v>
+        <v>13411003845.863</v>
       </c>
       <c r="L2">
-        <v>5167309070.354</v>
+        <v>11557481959.982</v>
       </c>
       <c r="M2">
-        <v>10109168684.993</v>
+        <v>15264525731.743</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>10479.598</v>
+        <v>39345.907</v>
       </c>
       <c r="C3">
-        <v>5724.228</v>
+        <v>24989.871</v>
       </c>
       <c r="D3">
-        <v>15234.968</v>
+        <v>53701.944</v>
       </c>
       <c r="E3">
-        <v>1529.678</v>
+        <v>5713.373</v>
       </c>
       <c r="F3">
-        <v>833.069</v>
+        <v>3635.594</v>
       </c>
       <c r="G3">
-        <v>2226.287</v>
+        <v>7791.152</v>
       </c>
       <c r="H3">
-        <v>583734563.5420001</v>
+        <v>2191645734.953</v>
       </c>
       <c r="I3">
-        <v>318850921.446</v>
+        <v>1391985772.306</v>
       </c>
       <c r="J3">
-        <v>848618205.6390001</v>
+        <v>2991305697.6</v>
       </c>
       <c r="K3">
-        <v>203447143.157</v>
+        <v>759878563.258</v>
       </c>
       <c r="L3">
-        <v>110798147.126</v>
+        <v>483533965.023</v>
       </c>
       <c r="M3">
-        <v>296096139.187</v>
+        <v>1036223161.493</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>781.931</v>
+        <v>1256.281</v>
       </c>
       <c r="C4">
-        <v>-18.997</v>
+        <v>44.867</v>
       </c>
       <c r="D4">
-        <v>1582.859</v>
+        <v>2467.695</v>
       </c>
       <c r="E4">
-        <v>209.515</v>
+        <v>350.194</v>
       </c>
       <c r="F4">
-        <v>-5.752</v>
+        <v>12.113</v>
       </c>
       <c r="G4">
-        <v>424.782</v>
+        <v>688.275</v>
       </c>
       <c r="H4">
-        <v>34473003.125</v>
+        <v>55385672.713</v>
       </c>
       <c r="I4">
-        <v>-837501.088</v>
+        <v>1978069.973</v>
       </c>
       <c r="J4">
-        <v>69783507.337</v>
+        <v>108793275.453</v>
       </c>
       <c r="K4">
-        <v>27865522.939</v>
+        <v>46575831.838</v>
       </c>
       <c r="L4">
-        <v>-764991.6459999999</v>
+        <v>1611078.974</v>
       </c>
       <c r="M4">
-        <v>56496037.523</v>
+        <v>91540584.70200001</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4899.426</v>
+        <v>30714.135</v>
       </c>
       <c r="C5">
-        <v>-104.235</v>
+        <v>1075.095</v>
       </c>
       <c r="D5">
-        <v>9903.087</v>
+        <v>60353.174</v>
       </c>
       <c r="E5">
-        <v>798.576</v>
+        <v>7644.511</v>
       </c>
       <c r="F5">
-        <v>-19.954</v>
+        <v>271.462</v>
       </c>
       <c r="G5">
-        <v>1617.106</v>
+        <v>15017.56</v>
       </c>
       <c r="H5">
-        <v>72545798.50399999</v>
+        <v>454784190.836</v>
       </c>
       <c r="I5">
-        <v>-1543406.331</v>
+        <v>15918927.572</v>
       </c>
       <c r="J5">
-        <v>146635003.34</v>
+        <v>893649454.101</v>
       </c>
       <c r="K5">
-        <v>106210622.09</v>
+        <v>1016719941.453</v>
       </c>
       <c r="L5">
-        <v>-2653871.699</v>
+        <v>36104462.509</v>
       </c>
       <c r="M5">
-        <v>215075115.878</v>
+        <v>1997335420.398</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>6351.143</v>
+        <v>6377.199</v>
       </c>
       <c r="C6">
-        <v>125.418</v>
+        <v>312.693</v>
       </c>
       <c r="D6">
-        <v>12576.868</v>
+        <v>12441.704</v>
       </c>
       <c r="E6">
-        <v>1482.707</v>
+        <v>2069.54</v>
       </c>
       <c r="F6">
-        <v>25.011</v>
+        <v>97.10899999999999</v>
       </c>
       <c r="G6">
-        <v>2940.403</v>
+        <v>4041.971</v>
       </c>
       <c r="H6">
-        <v>477612305.779</v>
+        <v>479571707.137</v>
       </c>
       <c r="I6">
-        <v>9431555.645</v>
+        <v>23514854.23</v>
       </c>
       <c r="J6">
-        <v>945793055.914</v>
+        <v>935628560.043</v>
       </c>
       <c r="K6">
-        <v>197200038.303</v>
+        <v>275248821.724</v>
       </c>
       <c r="L6">
-        <v>3326471.62</v>
+        <v>12915444.627</v>
       </c>
       <c r="M6">
-        <v>391073604.986</v>
+        <v>537582198.822</v>
       </c>
     </row>
     <row r="7">
@@ -643,40 +643,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>3559.966</v>
+        <v>13405.118</v>
       </c>
       <c r="C7">
-        <v>2166.182</v>
+        <v>9856.83</v>
       </c>
       <c r="D7">
-        <v>4953.749</v>
+        <v>16953.405</v>
       </c>
       <c r="E7">
-        <v>792.965</v>
+        <v>3431.747</v>
       </c>
       <c r="F7">
-        <v>481.228</v>
+        <v>2537.335</v>
       </c>
       <c r="G7">
-        <v>1104.701</v>
+        <v>4326.159</v>
       </c>
       <c r="H7">
-        <v>59946260.276</v>
+        <v>225728774.936</v>
       </c>
       <c r="I7">
-        <v>36476337.833</v>
+        <v>165979160.116</v>
       </c>
       <c r="J7">
-        <v>83416182.719</v>
+        <v>285478389.756</v>
       </c>
       <c r="K7">
-        <v>105464297.664</v>
+        <v>456422333.727</v>
       </c>
       <c r="L7">
-        <v>64003348.48</v>
+        <v>337465523.337</v>
       </c>
       <c r="M7">
-        <v>146925246.847</v>
+        <v>575379144.118</v>
       </c>
     </row>
     <row r="8">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>177893.116</v>
+        <v>151465.384</v>
       </c>
       <c r="C8">
-        <v>111987.082</v>
+        <v>115170.943</v>
       </c>
       <c r="D8">
-        <v>243799.15</v>
+        <v>187759.824</v>
       </c>
       <c r="E8">
-        <v>202271.477</v>
+        <v>148201.83</v>
       </c>
       <c r="F8">
-        <v>126799.228</v>
+        <v>112238.253</v>
       </c>
       <c r="G8">
-        <v>277743.726</v>
+        <v>184165.407</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26902106418.724</v>
+        <v>19710843413.588</v>
       </c>
       <c r="L8">
-        <v>16864297313.579</v>
+        <v>14927687688.997</v>
       </c>
       <c r="M8">
-        <v>36939915523.868</v>
+        <v>24493999138.179</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>203965.18</v>
+        <v>242564.024</v>
       </c>
       <c r="C9">
-        <v>119879.678</v>
+        <v>151450.299</v>
       </c>
       <c r="D9">
-        <v>288050.681</v>
+        <v>333677.746</v>
       </c>
       <c r="E9">
-        <v>207084.918</v>
+        <v>167411.195</v>
       </c>
       <c r="F9">
-        <v>128112.83</v>
+        <v>118791.866</v>
       </c>
       <c r="G9">
-        <v>286057.005</v>
+        <v>216030.524</v>
       </c>
       <c r="H9">
-        <v>1228311931.226</v>
+        <v>3407116080.575</v>
       </c>
       <c r="I9">
-        <v>362377907.505</v>
+        <v>1599376784.197</v>
       </c>
       <c r="J9">
-        <v>2094245954.949</v>
+        <v>5214855376.952999</v>
       </c>
       <c r="K9">
-        <v>27542294042.877</v>
+        <v>22265688905.588</v>
       </c>
       <c r="L9">
-        <v>17039006417.46</v>
+        <v>15799318163.467</v>
       </c>
       <c r="M9">
-        <v>38045581668.28899</v>
+        <v>28732059647.712</v>
       </c>
     </row>
     <row r="10">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B10">
-        <v>241531.634</v>
+        <v>301076.432</v>
       </c>
       <c r="C10">
-        <v>145658.94</v>
+        <v>201519.033</v>
       </c>
       <c r="D10">
-        <v>337404.327</v>
+        <v>400633.829</v>
       </c>
       <c r="E10">
-        <v>264515.286</v>
+        <v>268245.81</v>
       </c>
       <c r="F10">
-        <v>166964.778</v>
+        <v>205690.227</v>
       </c>
       <c r="G10">
-        <v>362065.792</v>
+        <v>330801.394</v>
       </c>
       <c r="H10">
-        <v>1228311931.226</v>
+        <v>3407116080.575</v>
       </c>
       <c r="I10">
-        <v>362377907.505</v>
+        <v>1599376784.197</v>
       </c>
       <c r="J10">
-        <v>2094245954.949</v>
+        <v>5214855376.952999</v>
       </c>
       <c r="K10">
-        <v>35180532920.55099</v>
+        <v>35676692751.451</v>
       </c>
       <c r="L10">
-        <v>22206315487.814</v>
+        <v>27356800123.44901</v>
       </c>
       <c r="M10">
-        <v>48154750353.282</v>
+        <v>43996585379.455</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -437,13 +437,13 @@
         <v>66956.083</v>
       </c>
       <c r="E2">
-        <v>100834.615</v>
+        <v>605007.692</v>
       </c>
       <c r="F2">
-        <v>86898.361</v>
+        <v>521390.164</v>
       </c>
       <c r="G2">
-        <v>114770.87</v>
+        <v>688625.221</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>13411003845.863</v>
+        <v>80466023075.175</v>
       </c>
       <c r="L2">
-        <v>11557481959.982</v>
+        <v>69344891759.894</v>
       </c>
       <c r="M2">
-        <v>15264525731.743</v>
+        <v>91587154390.457</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>53701.944</v>
       </c>
       <c r="E3">
-        <v>5713.373</v>
+        <v>34282.764</v>
       </c>
       <c r="F3">
-        <v>3635.594</v>
+        <v>21822.253</v>
       </c>
       <c r="G3">
-        <v>7791.152</v>
+        <v>46743.276</v>
       </c>
       <c r="H3">
         <v>2191645734.953</v>
@@ -498,314 +498,271 @@
         <v>2991305697.6</v>
       </c>
       <c r="K3">
-        <v>759878563.258</v>
+        <v>4559607654.604</v>
       </c>
       <c r="L3">
-        <v>483533965.023</v>
+        <v>2902359607.373</v>
       </c>
       <c r="M3">
-        <v>1036223161.493</v>
+        <v>6216855701.835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4">
-        <v>1256.281</v>
+        <v>30714.135</v>
       </c>
       <c r="C4">
-        <v>44.867</v>
+        <v>1075.095</v>
       </c>
       <c r="D4">
-        <v>2467.695</v>
+        <v>60353.174</v>
       </c>
       <c r="E4">
-        <v>350.194</v>
+        <v>45877.337</v>
       </c>
       <c r="F4">
-        <v>12.113</v>
+        <v>1614.897</v>
       </c>
       <c r="G4">
-        <v>688.275</v>
+        <v>90139.777</v>
       </c>
       <c r="H4">
-        <v>55385672.713</v>
+        <v>454784190.836</v>
       </c>
       <c r="I4">
-        <v>1978069.973</v>
+        <v>15918927.572</v>
       </c>
       <c r="J4">
-        <v>108793275.453</v>
+        <v>893649454.101</v>
       </c>
       <c r="K4">
-        <v>46575831.838</v>
+        <v>6101685877.592</v>
       </c>
       <c r="L4">
-        <v>1611078.974</v>
+        <v>214781364.787</v>
       </c>
       <c r="M4">
-        <v>91540584.70200001</v>
+        <v>11988590390.397</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B5">
-        <v>30714.135</v>
+        <v>6377.199</v>
       </c>
       <c r="C5">
-        <v>1075.095</v>
+        <v>312.693</v>
       </c>
       <c r="D5">
-        <v>60353.174</v>
+        <v>12441.704</v>
       </c>
       <c r="E5">
-        <v>7644.511</v>
+        <v>12420.895</v>
       </c>
       <c r="F5">
-        <v>271.462</v>
+        <v>581.563</v>
       </c>
       <c r="G5">
-        <v>15017.56</v>
+        <v>24260.226</v>
       </c>
       <c r="H5">
-        <v>454784190.836</v>
+        <v>479571707.137</v>
       </c>
       <c r="I5">
-        <v>15918927.572</v>
+        <v>23514854.23</v>
       </c>
       <c r="J5">
-        <v>893649454.101</v>
+        <v>935628560.043</v>
       </c>
       <c r="K5">
-        <v>1016719941.453</v>
+        <v>1651978993.529</v>
       </c>
       <c r="L5">
-        <v>36104462.509</v>
+        <v>77347895.376</v>
       </c>
       <c r="M5">
-        <v>1997335420.398</v>
+        <v>3226610091.683</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B6">
-        <v>6377.199</v>
+        <v>13405.118</v>
       </c>
       <c r="C6">
-        <v>312.693</v>
+        <v>9856.83</v>
       </c>
       <c r="D6">
-        <v>12441.704</v>
+        <v>16953.405</v>
       </c>
       <c r="E6">
-        <v>2069.54</v>
+        <v>20592.031</v>
       </c>
       <c r="F6">
-        <v>97.10899999999999</v>
+        <v>15223.442</v>
       </c>
       <c r="G6">
-        <v>4041.971</v>
+        <v>25960.621</v>
       </c>
       <c r="H6">
-        <v>479571707.137</v>
+        <v>225728774.936</v>
       </c>
       <c r="I6">
-        <v>23514854.23</v>
+        <v>165979160.116</v>
       </c>
       <c r="J6">
-        <v>935628560.043</v>
+        <v>285478389.756</v>
       </c>
       <c r="K6">
-        <v>275248821.724</v>
+        <v>2738740161.909</v>
       </c>
       <c r="L6">
-        <v>12915444.627</v>
+        <v>2024717760.449</v>
       </c>
       <c r="M6">
-        <v>537582198.822</v>
+        <v>3452762563.368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B7">
-        <v>13405.118</v>
+        <v>151465.384</v>
       </c>
       <c r="C7">
-        <v>9856.83</v>
+        <v>115170.943</v>
       </c>
       <c r="D7">
-        <v>16953.405</v>
+        <v>187759.824</v>
       </c>
       <c r="E7">
-        <v>3431.747</v>
+        <v>444411.416</v>
       </c>
       <c r="F7">
-        <v>2537.335</v>
+        <v>336634.859</v>
       </c>
       <c r="G7">
-        <v>4326.159</v>
+        <v>552187.972</v>
       </c>
       <c r="H7">
-        <v>225728774.936</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>165979160.116</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>285478389.756</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>456422333.727</v>
+        <v>59106718313.089</v>
       </c>
       <c r="L7">
-        <v>337465523.337</v>
+        <v>44772436287.516</v>
       </c>
       <c r="M7">
-        <v>575379144.118</v>
+        <v>73441000338.662</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B8">
-        <v>151465.384</v>
+        <v>241307.743</v>
       </c>
       <c r="C8">
-        <v>115170.943</v>
+        <v>151405.432</v>
       </c>
       <c r="D8">
-        <v>187759.824</v>
+        <v>331210.051</v>
       </c>
       <c r="E8">
-        <v>148201.83</v>
+        <v>557584.443</v>
       </c>
       <c r="F8">
-        <v>112238.253</v>
+        <v>375877.014</v>
       </c>
       <c r="G8">
-        <v>184165.407</v>
+        <v>739291.872</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3351730407.862</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1597398714.224</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>5106062101.499999</v>
       </c>
       <c r="K8">
-        <v>19710843413.588</v>
+        <v>74158731000.72299</v>
       </c>
       <c r="L8">
-        <v>14927687688.997</v>
+        <v>49991642915.501</v>
       </c>
       <c r="M8">
-        <v>24493999138.179</v>
+        <v>98325819085.94501</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>All</t>
         </is>
       </c>
       <c r="B9">
-        <v>242564.024</v>
+        <v>299820.151</v>
       </c>
       <c r="C9">
-        <v>151450.299</v>
+        <v>201474.166</v>
       </c>
       <c r="D9">
-        <v>333677.746</v>
+        <v>398166.134</v>
       </c>
       <c r="E9">
-        <v>167411.195</v>
+        <v>1162592.135</v>
       </c>
       <c r="F9">
-        <v>118791.866</v>
+        <v>897267.1780000001</v>
       </c>
       <c r="G9">
-        <v>216030.524</v>
+        <v>1427917.093</v>
       </c>
       <c r="H9">
-        <v>3407116080.575</v>
+        <v>3351730407.862</v>
       </c>
       <c r="I9">
-        <v>1599376784.197</v>
+        <v>1597398714.224</v>
       </c>
       <c r="J9">
-        <v>5214855376.952999</v>
+        <v>5106062101.499999</v>
       </c>
       <c r="K9">
-        <v>22265688905.588</v>
+        <v>154624754075.898</v>
       </c>
       <c r="L9">
-        <v>15799318163.467</v>
+        <v>119336534675.395</v>
       </c>
       <c r="M9">
-        <v>28732059647.712</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>301076.432</v>
-      </c>
-      <c r="C10">
-        <v>201519.033</v>
-      </c>
-      <c r="D10">
-        <v>400633.829</v>
-      </c>
-      <c r="E10">
-        <v>268245.81</v>
-      </c>
-      <c r="F10">
-        <v>205690.227</v>
-      </c>
-      <c r="G10">
-        <v>330801.394</v>
-      </c>
-      <c r="H10">
-        <v>3407116080.575</v>
-      </c>
-      <c r="I10">
-        <v>1599376784.197</v>
-      </c>
-      <c r="J10">
-        <v>5214855376.952999</v>
-      </c>
-      <c r="K10">
-        <v>35676692751.451</v>
-      </c>
-      <c r="L10">
-        <v>27356800123.44901</v>
-      </c>
-      <c r="M10">
-        <v>43996585379.455</v>
+        <v>189912973476.402</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
+++ b/output/Tables/2019/Resampling/HIA_per_disease_Rubin.xlsx
@@ -372,7 +372,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_sup</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -387,7 +387,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>tot_daly_sup</t>
+          <t>tot_daly_up</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -402,7 +402,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>tot_medic_costs_sup</t>
+          <t>tot_medic_costs_up</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>tot_soc_costs_sup</t>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
@@ -480,13 +480,13 @@
         <v>53701.944</v>
       </c>
       <c r="E3">
-        <v>34282.764</v>
+        <v>34282.845</v>
       </c>
       <c r="F3">
-        <v>21822.253</v>
+        <v>21815.601</v>
       </c>
       <c r="G3">
-        <v>46743.276</v>
+        <v>46750.09</v>
       </c>
       <c r="H3">
         <v>2191645734.953</v>
@@ -498,13 +498,13 @@
         <v>2991305697.6</v>
       </c>
       <c r="K3">
-        <v>4559607654.604</v>
+        <v>4559618399.063</v>
       </c>
       <c r="L3">
-        <v>2902359607.373</v>
+        <v>2901474873.62</v>
       </c>
       <c r="M3">
-        <v>6216855701.835</v>
+        <v>6217761924.505</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>60353.174</v>
       </c>
       <c r="E4">
-        <v>45877.337</v>
+        <v>45865.503</v>
       </c>
       <c r="F4">
-        <v>1614.897</v>
+        <v>1627.863</v>
       </c>
       <c r="G4">
-        <v>90139.777</v>
+        <v>90103.143</v>
       </c>
       <c r="H4">
         <v>454784190.836</v>
@@ -541,13 +541,13 @@
         <v>893649454.101</v>
       </c>
       <c r="K4">
-        <v>6101685877.592</v>
+        <v>6100111936.089</v>
       </c>
       <c r="L4">
-        <v>214781364.787</v>
+        <v>216505795.541</v>
       </c>
       <c r="M4">
-        <v>11988590390.397</v>
+        <v>11983718076.637</v>
       </c>
     </row>
     <row r="5">
@@ -566,13 +566,13 @@
         <v>12441.704</v>
       </c>
       <c r="E5">
-        <v>12420.895</v>
+        <v>12419.631</v>
       </c>
       <c r="F5">
-        <v>581.563</v>
+        <v>579.785</v>
       </c>
       <c r="G5">
-        <v>24260.226</v>
+        <v>24259.478</v>
       </c>
       <c r="H5">
         <v>479571707.137</v>
@@ -584,13 +584,13 @@
         <v>935628560.043</v>
       </c>
       <c r="K5">
-        <v>1651978993.529</v>
+        <v>1651810964.76</v>
       </c>
       <c r="L5">
-        <v>77347895.376</v>
+        <v>77111416.16500001</v>
       </c>
       <c r="M5">
-        <v>3226610091.683</v>
+        <v>3226510513.354</v>
       </c>
     </row>
     <row r="6">
@@ -609,13 +609,13 @@
         <v>16953.405</v>
       </c>
       <c r="E6">
-        <v>20592.031</v>
+        <v>20591.331</v>
       </c>
       <c r="F6">
-        <v>15223.442</v>
+        <v>15218.429</v>
       </c>
       <c r="G6">
-        <v>25960.621</v>
+        <v>25964.233</v>
       </c>
       <c r="H6">
         <v>225728774.936</v>
@@ -627,13 +627,13 @@
         <v>285478389.756</v>
       </c>
       <c r="K6">
-        <v>2738740161.909</v>
+        <v>2738647058.437</v>
       </c>
       <c r="L6">
-        <v>2024717760.449</v>
+        <v>2024051085.807</v>
       </c>
       <c r="M6">
-        <v>3452762563.368</v>
+        <v>3453243031.066</v>
       </c>
     </row>
     <row r="7">
@@ -652,13 +652,13 @@
         <v>187759.824</v>
       </c>
       <c r="E7">
-        <v>444411.416</v>
+        <v>444433.443</v>
       </c>
       <c r="F7">
-        <v>336634.859</v>
+        <v>336945.205</v>
       </c>
       <c r="G7">
-        <v>552187.972</v>
+        <v>551921.681</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>59106718313.089</v>
+        <v>59109647896.163</v>
       </c>
       <c r="L7">
-        <v>44772436287.516</v>
+        <v>44813712218.655</v>
       </c>
       <c r="M7">
-        <v>73441000338.662</v>
+        <v>73405583573.67</v>
       </c>
     </row>
     <row r="8">
@@ -695,13 +695,13 @@
         <v>331210.051</v>
       </c>
       <c r="E8">
-        <v>557584.443</v>
+        <v>557592.753</v>
       </c>
       <c r="F8">
-        <v>375877.014</v>
+        <v>376186.883</v>
       </c>
       <c r="G8">
-        <v>739291.872</v>
+        <v>738998.625</v>
       </c>
       <c r="H8">
         <v>3351730407.862</v>
@@ -713,13 +713,13 @@
         <v>5106062101.499999</v>
       </c>
       <c r="K8">
-        <v>74158731000.72299</v>
+        <v>74159836254.51201</v>
       </c>
       <c r="L8">
-        <v>49991642915.501</v>
+        <v>50032855389.78799</v>
       </c>
       <c r="M8">
-        <v>98325819085.94501</v>
+        <v>98286817119.23199</v>
       </c>
     </row>
     <row r="9">
@@ -738,13 +738,13 @@
         <v>398166.134</v>
       </c>
       <c r="E9">
-        <v>1162592.135</v>
+        <v>1162600.445</v>
       </c>
       <c r="F9">
-        <v>897267.1780000001</v>
+        <v>897577.047</v>
       </c>
       <c r="G9">
-        <v>1427917.093</v>
+        <v>1427623.846</v>
       </c>
       <c r="H9">
         <v>3351730407.862</v>
@@ -756,13 +756,13 @@
         <v>5106062101.499999</v>
       </c>
       <c r="K9">
-        <v>154624754075.898</v>
+        <v>154625859329.687</v>
       </c>
       <c r="L9">
-        <v>119336534675.395</v>
+        <v>119377747149.682</v>
       </c>
       <c r="M9">
-        <v>189912973476.402</v>
+        <v>189873971509.689</v>
       </c>
     </row>
   </sheetData>
